--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6FCE7B-2FB0-4D97-8392-44A8F3AA0738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE551E78-566C-436A-9CDF-91C3874DC436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="603">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1843,6 +1843,15 @@
   </si>
   <si>
     <t>https://i.ibb.co/VYj0ybqW/Lock-Chip-Bahamut.png</t>
+  </si>
+  <si>
+    <t>Spin Direction</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
   </si>
 </sst>
 </file>
@@ -4155,1077 +4164,1368 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="B1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C1" t="s">
         <v>594</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>249</v>
       </c>
       <c r="B2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" t="s">
         <v>595</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>251</v>
       </c>
       <c r="B4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C4" t="s">
+        <v>596</v>
+      </c>
+      <c r="D4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>253</v>
       </c>
       <c r="B6" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>254</v>
       </c>
       <c r="B7" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C7" t="s">
+        <v>596</v>
+      </c>
+      <c r="D7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>255</v>
       </c>
       <c r="B8" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>256</v>
       </c>
       <c r="B9" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C9" t="s">
+        <v>596</v>
+      </c>
+      <c r="D9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>257</v>
       </c>
       <c r="B10" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C10" t="s">
+        <v>596</v>
+      </c>
+      <c r="D10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>258</v>
       </c>
       <c r="B11" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C11" t="s">
+        <v>596</v>
+      </c>
+      <c r="D11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C12" t="s">
+        <v>596</v>
+      </c>
+      <c r="D12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>260</v>
       </c>
       <c r="B13" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C13" t="s">
+        <v>596</v>
+      </c>
+      <c r="D13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>261</v>
       </c>
       <c r="B14" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C14" t="s">
+        <v>596</v>
+      </c>
+      <c r="D14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>262</v>
       </c>
       <c r="B15" t="s">
+        <v>602</v>
+      </c>
+      <c r="C15" t="s">
         <v>595</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>263</v>
       </c>
       <c r="B16" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C16" t="s">
+        <v>596</v>
+      </c>
+      <c r="D16" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>264</v>
       </c>
       <c r="B17" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C17" t="s">
+        <v>596</v>
+      </c>
+      <c r="D17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>265</v>
       </c>
       <c r="B18" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C18" t="s">
+        <v>596</v>
+      </c>
+      <c r="D18" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>266</v>
       </c>
       <c r="B19" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C19" t="s">
+        <v>596</v>
+      </c>
+      <c r="D19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>267</v>
       </c>
       <c r="B20" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C20" t="s">
+        <v>596</v>
+      </c>
+      <c r="D20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>268</v>
       </c>
       <c r="B21" t="s">
+        <v>602</v>
+      </c>
+      <c r="C21" t="s">
         <v>595</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>269</v>
       </c>
       <c r="B22" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C22" t="s">
+        <v>596</v>
+      </c>
+      <c r="D22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>270</v>
       </c>
       <c r="B23" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C23" t="s">
+        <v>596</v>
+      </c>
+      <c r="D23" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>271</v>
       </c>
       <c r="B24" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C24" t="s">
+        <v>596</v>
+      </c>
+      <c r="D24" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>272</v>
       </c>
       <c r="B25" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C25" t="s">
+        <v>596</v>
+      </c>
+      <c r="D25" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>273</v>
       </c>
       <c r="B26" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C26" t="s">
+        <v>596</v>
+      </c>
+      <c r="D26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>274</v>
       </c>
       <c r="B27" t="s">
+        <v>602</v>
+      </c>
+      <c r="C27" t="s">
         <v>595</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>275</v>
       </c>
       <c r="B28" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C28" t="s">
+        <v>596</v>
+      </c>
+      <c r="D28" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>276</v>
       </c>
       <c r="B29" t="s">
+        <v>602</v>
+      </c>
+      <c r="C29" t="s">
         <v>595</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>277</v>
       </c>
       <c r="B30" t="s">
+        <v>602</v>
+      </c>
+      <c r="C30" t="s">
         <v>595</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>278</v>
       </c>
       <c r="B31" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C31" t="s">
+        <v>596</v>
+      </c>
+      <c r="D31" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>279</v>
       </c>
       <c r="B32" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C32" t="s">
+        <v>596</v>
+      </c>
+      <c r="D32" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>280</v>
       </c>
       <c r="B33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C33" t="s">
         <v>595</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>281</v>
       </c>
       <c r="B34" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C34" t="s">
+        <v>596</v>
+      </c>
+      <c r="D34" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>282</v>
       </c>
       <c r="B35" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C35" t="s">
+        <v>596</v>
+      </c>
+      <c r="D35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>283</v>
       </c>
       <c r="B36" t="s">
+        <v>602</v>
+      </c>
+      <c r="C36" t="s">
         <v>595</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>284</v>
       </c>
       <c r="B37" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C37" t="s">
+        <v>596</v>
+      </c>
+      <c r="D37" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>285</v>
       </c>
       <c r="B38" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C38" t="s">
+        <v>596</v>
+      </c>
+      <c r="D38" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>286</v>
       </c>
       <c r="B39" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C39" t="s">
+        <v>596</v>
+      </c>
+      <c r="D39" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>287</v>
       </c>
       <c r="B40" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C40" t="s">
+        <v>596</v>
+      </c>
+      <c r="D40" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>288</v>
       </c>
       <c r="B41" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C41" t="s">
+        <v>596</v>
+      </c>
+      <c r="D41" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>289</v>
       </c>
       <c r="B42" t="s">
+        <v>601</v>
+      </c>
+      <c r="C42" t="s">
         <v>595</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>290</v>
       </c>
       <c r="B43" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C43" t="s">
+        <v>596</v>
+      </c>
+      <c r="D43" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>291</v>
       </c>
       <c r="B44" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C44" t="s">
+        <v>596</v>
+      </c>
+      <c r="D44" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>292</v>
       </c>
       <c r="B45" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C45" t="s">
+        <v>596</v>
+      </c>
+      <c r="D45" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>293</v>
       </c>
       <c r="B46" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C46" t="s">
+        <v>596</v>
+      </c>
+      <c r="D46" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>294</v>
       </c>
       <c r="B47" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C47" t="s">
+        <v>596</v>
+      </c>
+      <c r="D47" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>295</v>
       </c>
       <c r="B48" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C48" t="s">
+        <v>596</v>
+      </c>
+      <c r="D48" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>296</v>
       </c>
       <c r="B49" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C49" t="s">
+        <v>596</v>
+      </c>
+      <c r="D49" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>297</v>
       </c>
       <c r="B50" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C50" t="s">
+        <v>596</v>
+      </c>
+      <c r="D50" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>298</v>
       </c>
       <c r="B51" t="s">
+        <v>602</v>
+      </c>
+      <c r="C51" t="s">
         <v>595</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>299</v>
       </c>
       <c r="B52" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C52" t="s">
+        <v>596</v>
+      </c>
+      <c r="D52" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>300</v>
       </c>
       <c r="B53" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C53" t="s">
+        <v>596</v>
+      </c>
+      <c r="D53" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>301</v>
       </c>
       <c r="B54" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C54" t="s">
+        <v>596</v>
+      </c>
+      <c r="D54" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>302</v>
       </c>
       <c r="B55" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C55" t="s">
+        <v>596</v>
+      </c>
+      <c r="D55" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>303</v>
       </c>
       <c r="B56" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C56" t="s">
+        <v>596</v>
+      </c>
+      <c r="D56" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>304</v>
       </c>
       <c r="B57" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C57" t="s">
+        <v>596</v>
+      </c>
+      <c r="D57" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>305</v>
       </c>
       <c r="B58" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C58" t="s">
+        <v>596</v>
+      </c>
+      <c r="D58" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>306</v>
       </c>
       <c r="B59" t="s">
+        <v>602</v>
+      </c>
+      <c r="C59" t="s">
         <v>595</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>307</v>
       </c>
       <c r="B60" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C60" t="s">
+        <v>596</v>
+      </c>
+      <c r="D60" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>308</v>
       </c>
       <c r="B61" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C61" t="s">
+        <v>596</v>
+      </c>
+      <c r="D61" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>309</v>
       </c>
       <c r="B62" t="s">
+        <v>602</v>
+      </c>
+      <c r="C62" t="s">
         <v>595</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>310</v>
       </c>
       <c r="B63" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C63" t="s">
+        <v>596</v>
+      </c>
+      <c r="D63" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>311</v>
       </c>
       <c r="B64" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C64" t="s">
+        <v>596</v>
+      </c>
+      <c r="D64" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>312</v>
       </c>
       <c r="B65" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C65" t="s">
+        <v>596</v>
+      </c>
+      <c r="D65" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>313</v>
       </c>
       <c r="B66" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C66" t="s">
+        <v>596</v>
+      </c>
+      <c r="D66" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>314</v>
       </c>
       <c r="B67" t="s">
+        <v>602</v>
+      </c>
+      <c r="C67" t="s">
         <v>595</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>315</v>
       </c>
       <c r="B68" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C68" t="s">
+        <v>596</v>
+      </c>
+      <c r="D68" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>316</v>
       </c>
       <c r="B69" t="s">
+        <v>602</v>
+      </c>
+      <c r="C69" t="s">
         <v>595</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>317</v>
       </c>
       <c r="B70" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C70" t="s">
+        <v>596</v>
+      </c>
+      <c r="D70" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>318</v>
       </c>
       <c r="B71" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C71" t="s">
+        <v>596</v>
+      </c>
+      <c r="D71" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>319</v>
       </c>
       <c r="B72" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C72" t="s">
+        <v>596</v>
+      </c>
+      <c r="D72" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>320</v>
       </c>
       <c r="B73" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C73" t="s">
+        <v>596</v>
+      </c>
+      <c r="D73" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>321</v>
       </c>
       <c r="B74" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C74" t="s">
+        <v>596</v>
+      </c>
+      <c r="D74" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>322</v>
       </c>
       <c r="B75" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C75" t="s">
+        <v>596</v>
+      </c>
+      <c r="D75" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>323</v>
       </c>
       <c r="B76" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C76" t="s">
+        <v>596</v>
+      </c>
+      <c r="D76" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>324</v>
       </c>
       <c r="B77" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C77" t="s">
+        <v>596</v>
+      </c>
+      <c r="D77" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>325</v>
       </c>
       <c r="B78" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C78" t="s">
+        <v>596</v>
+      </c>
+      <c r="D78" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>326</v>
       </c>
       <c r="B79" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C79" t="s">
+        <v>596</v>
+      </c>
+      <c r="D79" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>327</v>
       </c>
       <c r="B80" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C80" t="s">
+        <v>596</v>
+      </c>
+      <c r="D80" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>328</v>
       </c>
       <c r="B81" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C81" t="s">
+        <v>596</v>
+      </c>
+      <c r="D81" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>329</v>
       </c>
       <c r="B82" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C82" t="s">
+        <v>596</v>
+      </c>
+      <c r="D82" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>330</v>
       </c>
       <c r="B83" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C83" t="s">
+        <v>596</v>
+      </c>
+      <c r="D83" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>331</v>
       </c>
       <c r="B84" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C84" t="s">
+        <v>596</v>
+      </c>
+      <c r="D84" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>332</v>
       </c>
       <c r="B85" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C85" t="s">
+        <v>596</v>
+      </c>
+      <c r="D85" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>333</v>
       </c>
       <c r="B86" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C86" t="s">
+        <v>596</v>
+      </c>
+      <c r="D86" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>334</v>
       </c>
       <c r="B87" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C87" t="s">
+        <v>596</v>
+      </c>
+      <c r="D87" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>335</v>
       </c>
       <c r="B88" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C88" t="s">
+        <v>596</v>
+      </c>
+      <c r="D88" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>336</v>
       </c>
       <c r="B89" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C89" t="s">
+        <v>596</v>
+      </c>
+      <c r="D89" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>337</v>
       </c>
       <c r="B90" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C90" t="s">
+        <v>596</v>
+      </c>
+      <c r="D90" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>338</v>
       </c>
       <c r="B91" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C91" t="s">
+        <v>596</v>
+      </c>
+      <c r="D91" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>339</v>
       </c>
       <c r="B92" t="s">
+        <v>602</v>
+      </c>
+      <c r="C92" t="s">
         <v>595</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>340</v>
       </c>
       <c r="B93" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C93" t="s">
+        <v>596</v>
+      </c>
+      <c r="D93" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>341</v>
       </c>
       <c r="B94" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C94" t="s">
+        <v>596</v>
+      </c>
+      <c r="D94" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>342</v>
       </c>
       <c r="B95" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C95" t="s">
+        <v>596</v>
+      </c>
+      <c r="D95" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>343</v>
       </c>
       <c r="B96" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C96" t="s">
+        <v>596</v>
+      </c>
+      <c r="D96" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>589</v>
       </c>
       <c r="B97" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C97" t="s">
+        <v>596</v>
+      </c>
+      <c r="D97" t="s">
         <v>590</v>
       </c>
     </row>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE551E78-566C-436A-9CDF-91C3874DC436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFF5216-B205-4268-9FCD-E1FAC28C6925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="605">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1852,6 +1852,12 @@
   </si>
   <si>
     <t>Right</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/dsgRZxd8/Assist-Blade-Free.png</t>
   </si>
 </sst>
 </file>
@@ -5775,7 +5781,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5880,6 +5886,14 @@
       </c>
       <c r="B13" t="s">
         <v>598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>603</v>
+      </c>
+      <c r="B14" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFF5216-B205-4268-9FCD-E1FAC28C6925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EB351C-512B-407A-909F-D0535D9E50C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -5067,7 +5067,7 @@
         <v>602</v>
       </c>
       <c r="C64" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D64" t="s">
         <v>187</v>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EB351C-512B-407A-909F-D0535D9E50C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96527CB6-0D79-46A1-919C-7839BE259B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="2505" windowWidth="25500" windowHeight="18375" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="607">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1858,6 +1858,12 @@
   </si>
   <si>
     <t>https://i.ibb.co/dsgRZxd8/Assist-Blade-Free.png</t>
+  </si>
+  <si>
+    <t>Zillian</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/0pxp5Bt7/Assist-Blade-Zillion.png</t>
   </si>
 </sst>
 </file>
@@ -5781,7 +5787,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5894,6 +5900,14 @@
       </c>
       <c r="B14" t="s">
         <v>604</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>605</v>
+      </c>
+      <c r="B15" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96527CB6-0D79-46A1-919C-7839BE259B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12A3AE7-DD0E-41EF-BA95-3B216DE0619D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="2505" windowWidth="25500" windowHeight="18375" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -4821,7 +4821,7 @@
         <v>602</v>
       </c>
       <c r="C46" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D46" t="s">
         <v>156</v>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12A3AE7-DD0E-41EF-BA95-3B216DE0619D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD553AC-1F09-4A25-9360-AEDCE0F729D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
     <sheet name="Lock Chips" sheetId="2" r:id="rId2"/>
     <sheet name="Blades BX-UX" sheetId="3" r:id="rId3"/>
-    <sheet name="Blades CX" sheetId="4" r:id="rId4"/>
-    <sheet name="Over Blades" sheetId="5" r:id="rId5"/>
-    <sheet name="Metal Blades" sheetId="6" r:id="rId6"/>
-    <sheet name="Assist Blades" sheetId="7" r:id="rId7"/>
-    <sheet name="Ratchets" sheetId="8" r:id="rId8"/>
-    <sheet name="Bits" sheetId="9" r:id="rId9"/>
-    <sheet name="Category" sheetId="10" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId11"/>
+    <sheet name="Blades UX-Expanded" sheetId="12" r:id="rId4"/>
+    <sheet name="Blades CX" sheetId="4" r:id="rId5"/>
+    <sheet name="Over Blades" sheetId="5" r:id="rId6"/>
+    <sheet name="Metal Blades" sheetId="6" r:id="rId7"/>
+    <sheet name="Assist Blades" sheetId="7" r:id="rId8"/>
+    <sheet name="Ratchets" sheetId="8" r:id="rId9"/>
+    <sheet name="Bits" sheetId="9" r:id="rId10"/>
+    <sheet name="Category" sheetId="10" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="615">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1864,6 +1865,30 @@
   </si>
   <si>
     <t>https://i.ibb.co/0pxp5Bt7/Assist-Blade-Zillion.png</t>
+  </si>
+  <si>
+    <t>Turbo</t>
+  </si>
+  <si>
+    <t>Operate</t>
+  </si>
+  <si>
+    <t>Bullet Gryphon</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/TMqzPBZB/Ratchet-Bit-Turbo.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/27cJyxqP/Ratchet-Bit-Operate-29.png</t>
+  </si>
+  <si>
+    <t>Tr</t>
+  </si>
+  <si>
+    <t>Op</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/ccVD1jm3/Ratchet-Blade-Bullet-Griffon.png</t>
   </si>
 </sst>
 </file>
@@ -3372,6 +3397,548 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>427</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>431</v>
+      </c>
+      <c r="B10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>433</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>441</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>443</v>
+      </c>
+      <c r="B16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>445</v>
+      </c>
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>447</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>449</v>
+      </c>
+      <c r="B19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>453</v>
+      </c>
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>455</v>
+      </c>
+      <c r="B22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>457</v>
+      </c>
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>459</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>461</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>463</v>
+      </c>
+      <c r="B26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>465</v>
+      </c>
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>467</v>
+      </c>
+      <c r="B28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>469</v>
+      </c>
+      <c r="B29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>471</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>473</v>
+      </c>
+      <c r="B31" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>475</v>
+      </c>
+      <c r="B32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>477</v>
+      </c>
+      <c r="B33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>479</v>
+      </c>
+      <c r="B34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>481</v>
+      </c>
+      <c r="B35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>483</v>
+      </c>
+      <c r="B36" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>485</v>
+      </c>
+      <c r="B37" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>487</v>
+      </c>
+      <c r="B38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>489</v>
+      </c>
+      <c r="B39" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>491</v>
+      </c>
+      <c r="B40" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>493</v>
+      </c>
+      <c r="B41" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>495</v>
+      </c>
+      <c r="B42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>497</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>499</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>501</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>591</v>
+      </c>
+      <c r="B46" t="s">
+        <v>593</v>
+      </c>
+      <c r="C46" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>607</v>
+      </c>
+      <c r="B47" t="s">
+        <v>610</v>
+      </c>
+      <c r="C47" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>608</v>
+      </c>
+      <c r="B48" t="s">
+        <v>611</v>
+      </c>
+      <c r="C48" t="s">
+        <v>613</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3439,7 +4006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5548,6 +6115,43 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E061927E-DAF7-4362-80C4-8054C331DDF2}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5701,7 +6305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5743,7 +6347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5785,7 +6389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5915,7 +6519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6211,524 +6815,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>419</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>421</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>423</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>425</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>427</v>
-      </c>
-      <c r="B8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>429</v>
-      </c>
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>431</v>
-      </c>
-      <c r="B10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>433</v>
-      </c>
-      <c r="B11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>435</v>
-      </c>
-      <c r="B12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>437</v>
-      </c>
-      <c r="B13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>439</v>
-      </c>
-      <c r="B14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>441</v>
-      </c>
-      <c r="B15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>443</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>445</v>
-      </c>
-      <c r="B17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>447</v>
-      </c>
-      <c r="B18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>449</v>
-      </c>
-      <c r="B19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>451</v>
-      </c>
-      <c r="B20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>453</v>
-      </c>
-      <c r="B21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>455</v>
-      </c>
-      <c r="B22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>457</v>
-      </c>
-      <c r="B23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>459</v>
-      </c>
-      <c r="B24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>461</v>
-      </c>
-      <c r="B25" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>463</v>
-      </c>
-      <c r="B26" t="s">
-        <v>144</v>
-      </c>
-      <c r="C26" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>465</v>
-      </c>
-      <c r="B27" t="s">
-        <v>149</v>
-      </c>
-      <c r="C27" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>467</v>
-      </c>
-      <c r="B28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>469</v>
-      </c>
-      <c r="B29" t="s">
-        <v>157</v>
-      </c>
-      <c r="C29" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>471</v>
-      </c>
-      <c r="B30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>473</v>
-      </c>
-      <c r="B31" t="s">
-        <v>169</v>
-      </c>
-      <c r="C31" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>475</v>
-      </c>
-      <c r="B32" t="s">
-        <v>170</v>
-      </c>
-      <c r="C32" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>477</v>
-      </c>
-      <c r="B33" t="s">
-        <v>181</v>
-      </c>
-      <c r="C33" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>479</v>
-      </c>
-      <c r="B34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>481</v>
-      </c>
-      <c r="B35" t="s">
-        <v>196</v>
-      </c>
-      <c r="C35" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>483</v>
-      </c>
-      <c r="B36" t="s">
-        <v>209</v>
-      </c>
-      <c r="C36" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>485</v>
-      </c>
-      <c r="B37" t="s">
-        <v>212</v>
-      </c>
-      <c r="C37" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>487</v>
-      </c>
-      <c r="B38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>489</v>
-      </c>
-      <c r="B39" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>491</v>
-      </c>
-      <c r="B40" t="s">
-        <v>220</v>
-      </c>
-      <c r="C40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>493</v>
-      </c>
-      <c r="B41" t="s">
-        <v>222</v>
-      </c>
-      <c r="C41" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>495</v>
-      </c>
-      <c r="B42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>497</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>499</v>
-      </c>
-      <c r="B44" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>501</v>
-      </c>
-      <c r="B45" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>591</v>
-      </c>
-      <c r="B46" t="s">
-        <v>593</v>
-      </c>
-      <c r="C46" t="s">
-        <v>592</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD553AC-1F09-4A25-9360-AEDCE0F729D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E4508E-D8C9-4C4E-A0BA-28A9EEEC8027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1873,9 +1873,6 @@
     <t>Operate</t>
   </si>
   <si>
-    <t>Bullet Gryphon</t>
-  </si>
-  <si>
     <t>https://i.ibb.co/TMqzPBZB/Ratchet-Bit-Turbo.png</t>
   </si>
   <si>
@@ -1889,6 +1886,9 @@
   </si>
   <si>
     <t>https://i.ibb.co/ccVD1jm3/Ratchet-Blade-Bullet-Griffon.png</t>
+  </si>
+  <si>
+    <t>Bullet Griphon</t>
   </si>
 </sst>
 </file>
@@ -3916,10 +3916,10 @@
         <v>607</v>
       </c>
       <c r="B47" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C47" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -3927,10 +3927,10 @@
         <v>608</v>
       </c>
       <c r="B48" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C48" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -6137,13 +6137,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B2" t="s">
         <v>602</v>
       </c>
       <c r="C2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E4508E-D8C9-4C4E-A0BA-28A9EEEC8027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F61FD8-F367-4D57-B8C4-4068306248AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="617">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1889,6 +1889,12 @@
   </si>
   <si>
     <t>Bullet Griphon</t>
+  </si>
+  <si>
+    <t>StormSpriggan</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/RkChfDqK/Storm-Spriggan-2-70-M.png</t>
   </si>
 </sst>
 </file>
@@ -4743,7 +4749,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -6106,6 +6112,20 @@
       </c>
       <c r="D97" t="s">
         <v>590</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>615</v>
+      </c>
+      <c r="B98" t="s">
+        <v>602</v>
+      </c>
+      <c r="C98" t="s">
+        <v>596</v>
+      </c>
+      <c r="D98" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F61FD8-F367-4D57-B8C4-4068306248AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B59C77-103C-4274-8049-1C9F1CB2544C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="619">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1895,6 +1895,12 @@
   </si>
   <si>
     <t>https://i.ibb.co/RkChfDqK/Storm-Spriggan-2-70-M.png</t>
+  </si>
+  <si>
+    <t>Assault</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/8Dx0bRyT/assault-2-70-M.png</t>
   </si>
 </sst>
 </file>
@@ -6411,7 +6417,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6532,6 +6538,14 @@
       </c>
       <c r="B15" t="s">
         <v>606</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>617</v>
+      </c>
+      <c r="B16" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B59C77-103C-4274-8049-1C9F1CB2544C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC262F50-EE30-434D-8F88-E73B53CE77E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="621">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1901,6 +1901,12 @@
   </si>
   <si>
     <t>https://i.ibb.co/8Dx0bRyT/assault-2-70-M.png</t>
+  </si>
+  <si>
+    <t>Sol</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/6RhzCmTn/Lock-Chip-Sol.png</t>
   </si>
 </sst>
 </file>
@@ -4593,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4746,6 +4752,14 @@
       </c>
       <c r="B19" t="s">
         <v>588</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>619</v>
+      </c>
+      <c r="B20" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC262F50-EE30-434D-8F88-E73B53CE77E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD05B59C-E7C7-4C1D-9E5C-4E6822BCDB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="623">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1907,6 +1907,12 @@
   </si>
   <si>
     <t>https://i.ibb.co/6RhzCmTn/Lock-Chip-Sol.png</t>
+  </si>
+  <si>
+    <t>Dual</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/BV5Rc8xj/Assist-Blade-Dual-29.png</t>
   </si>
 </sst>
 </file>
@@ -6431,7 +6437,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6560,6 +6566,14 @@
       </c>
       <c r="B16" t="s">
         <v>618</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>621</v>
+      </c>
+      <c r="B17" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD05B59C-E7C7-4C1D-9E5C-4E6822BCDB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E1439A-FE33-41F0-9D5C-3E70CA2C0482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -5098,7 +5098,7 @@
         <v>602</v>
       </c>
       <c r="C23" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D23" t="s">
         <v>111</v>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E1439A-FE33-41F0-9D5C-3E70CA2C0482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Category" sheetId="10" r:id="rId11"/>
     <sheet name="Sheet1" sheetId="11" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="638">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1913,16 +1913,57 @@
   </si>
   <si>
     <t>https://i.ibb.co/BV5Rc8xj/Assist-Blade-Dual-29.png</t>
+  </si>
+  <si>
+    <t>Unicorn</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Peak</t>
+  </si>
+  <si>
+    <t>Gear Unite</t>
+  </si>
+  <si>
+    <t>GU</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/WNXdZTmc/IMG-7496.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/QzFTs2j/IMG-7491.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/DP9JDrRj/IMG-7492.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/KjRGwBFj/IMG-7494.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/7tbGH5FS/IMG-7493.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1945,13 +1986,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2253,1164 +2300,1164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A232"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>229</v>
       </c>
@@ -3422,14 +3469,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>412</v>
       </c>
@@ -3440,7 +3487,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>415</v>
       </c>
@@ -3451,7 +3498,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>417</v>
       </c>
@@ -3462,7 +3509,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>419</v>
       </c>
@@ -3473,7 +3520,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>421</v>
       </c>
@@ -3484,7 +3531,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>423</v>
       </c>
@@ -3495,7 +3542,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>425</v>
       </c>
@@ -3506,7 +3553,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>427</v>
       </c>
@@ -3517,7 +3564,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>429</v>
       </c>
@@ -3528,7 +3575,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>431</v>
       </c>
@@ -3539,7 +3586,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>433</v>
       </c>
@@ -3550,7 +3597,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>435</v>
       </c>
@@ -3561,7 +3608,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>437</v>
       </c>
@@ -3572,7 +3619,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>439</v>
       </c>
@@ -3583,7 +3630,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>441</v>
       </c>
@@ -3594,7 +3641,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>443</v>
       </c>
@@ -3605,7 +3652,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>445</v>
       </c>
@@ -3616,7 +3663,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>447</v>
       </c>
@@ -3627,7 +3674,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>449</v>
       </c>
@@ -3638,7 +3685,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>451</v>
       </c>
@@ -3649,7 +3696,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>453</v>
       </c>
@@ -3660,7 +3707,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>455</v>
       </c>
@@ -3671,7 +3718,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>457</v>
       </c>
@@ -3682,7 +3729,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>459</v>
       </c>
@@ -3693,7 +3740,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>461</v>
       </c>
@@ -3704,7 +3751,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>463</v>
       </c>
@@ -3715,7 +3762,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>465</v>
       </c>
@@ -3726,7 +3773,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>467</v>
       </c>
@@ -3737,7 +3784,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>469</v>
       </c>
@@ -3748,7 +3795,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>471</v>
       </c>
@@ -3759,7 +3806,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>473</v>
       </c>
@@ -3770,7 +3817,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>475</v>
       </c>
@@ -3781,7 +3828,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>477</v>
       </c>
@@ -3792,7 +3839,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>479</v>
       </c>
@@ -3803,7 +3850,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>481</v>
       </c>
@@ -3814,7 +3861,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>483</v>
       </c>
@@ -3825,7 +3872,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>485</v>
       </c>
@@ -3836,7 +3883,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>487</v>
       </c>
@@ -3847,7 +3894,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>489</v>
       </c>
@@ -3858,7 +3905,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>491</v>
       </c>
@@ -3869,7 +3916,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>493</v>
       </c>
@@ -3880,7 +3927,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>495</v>
       </c>
@@ -3891,7 +3938,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>497</v>
       </c>
@@ -3902,7 +3949,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>499</v>
       </c>
@@ -3913,7 +3960,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>501</v>
       </c>
@@ -3924,7 +3971,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>591</v>
       </c>
@@ -3935,7 +3982,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>607</v>
       </c>
@@ -3946,7 +3993,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>608</v>
       </c>
@@ -3957,7 +4004,21 @@
         <v>612</v>
       </c>
     </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>627</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C49" t="s">
+        <v>628</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B49" r:id="rId1" xr:uid="{929ABBCD-DB33-CA40-B51B-5CEE287D6DEF}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3965,9 +4026,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -3975,52 +4036,52 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>512</v>
       </c>
@@ -4033,12 +4094,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>513</v>
       </c>
@@ -4046,7 +4107,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>515</v>
       </c>
@@ -4054,7 +4115,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>517</v>
       </c>
@@ -4062,7 +4123,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>519</v>
       </c>
@@ -4070,7 +4131,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>520</v>
       </c>
@@ -4078,7 +4139,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>521</v>
       </c>
@@ -4086,7 +4147,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>522</v>
       </c>
@@ -4094,7 +4155,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>523</v>
       </c>
@@ -4102,7 +4163,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>524</v>
       </c>
@@ -4110,7 +4171,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>525</v>
       </c>
@@ -4118,7 +4179,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>526</v>
       </c>
@@ -4126,7 +4187,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>527</v>
       </c>
@@ -4134,7 +4195,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>528</v>
       </c>
@@ -4142,7 +4203,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>529</v>
       </c>
@@ -4150,7 +4211,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>530</v>
       </c>
@@ -4158,7 +4219,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>531</v>
       </c>
@@ -4166,7 +4227,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>532</v>
       </c>
@@ -4174,7 +4235,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>533</v>
       </c>
@@ -4182,7 +4243,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>534</v>
       </c>
@@ -4190,7 +4251,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>535</v>
       </c>
@@ -4198,7 +4259,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>536</v>
       </c>
@@ -4206,7 +4267,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>537</v>
       </c>
@@ -4214,7 +4275,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>538</v>
       </c>
@@ -4222,7 +4283,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>539</v>
       </c>
@@ -4230,7 +4291,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>540</v>
       </c>
@@ -4238,7 +4299,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>541</v>
       </c>
@@ -4246,7 +4307,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>542</v>
       </c>
@@ -4254,7 +4315,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>543</v>
       </c>
@@ -4262,7 +4323,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>544</v>
       </c>
@@ -4270,7 +4331,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>545</v>
       </c>
@@ -4278,7 +4339,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>546</v>
       </c>
@@ -4286,7 +4347,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>547</v>
       </c>
@@ -4294,7 +4355,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>548</v>
       </c>
@@ -4302,7 +4363,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>549</v>
       </c>
@@ -4310,7 +4371,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>550</v>
       </c>
@@ -4318,7 +4379,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>551</v>
       </c>
@@ -4326,7 +4387,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>552</v>
       </c>
@@ -4334,7 +4395,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>553</v>
       </c>
@@ -4342,7 +4403,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>554</v>
       </c>
@@ -4350,7 +4411,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>555</v>
       </c>
@@ -4358,7 +4419,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>556</v>
       </c>
@@ -4366,7 +4427,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>557</v>
       </c>
@@ -4374,7 +4435,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>558</v>
       </c>
@@ -4382,7 +4443,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>559</v>
       </c>
@@ -4390,7 +4451,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>560</v>
       </c>
@@ -4398,7 +4459,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>561</v>
       </c>
@@ -4406,7 +4467,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>562</v>
       </c>
@@ -4414,7 +4475,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>563</v>
       </c>
@@ -4422,7 +4483,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>564</v>
       </c>
@@ -4430,7 +4491,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>565</v>
       </c>
@@ -4438,7 +4499,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>566</v>
       </c>
@@ -4446,7 +4507,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>567</v>
       </c>
@@ -4454,7 +4515,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>568</v>
       </c>
@@ -4462,7 +4523,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>569</v>
       </c>
@@ -4470,7 +4531,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>570</v>
       </c>
@@ -4478,7 +4539,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>571</v>
       </c>
@@ -4486,7 +4547,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>572</v>
       </c>
@@ -4494,7 +4555,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>573</v>
       </c>
@@ -4502,7 +4563,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>574</v>
       </c>
@@ -4510,7 +4571,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>575</v>
       </c>
@@ -4518,7 +4579,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>576</v>
       </c>
@@ -4526,7 +4587,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>577</v>
       </c>
@@ -4534,7 +4595,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>578</v>
       </c>
@@ -4542,7 +4603,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>579</v>
       </c>
@@ -4550,7 +4611,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>580</v>
       </c>
@@ -4558,7 +4619,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>581</v>
       </c>
@@ -4566,7 +4627,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>582</v>
       </c>
@@ -4574,7 +4635,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>583</v>
       </c>
@@ -4582,7 +4643,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>584</v>
       </c>
@@ -4590,7 +4651,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>585</v>
       </c>
@@ -4605,10 +4666,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -4616,7 +4677,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>232</v>
       </c>
@@ -4624,7 +4685,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>233</v>
       </c>
@@ -4632,7 +4693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>234</v>
       </c>
@@ -4640,7 +4701,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>235</v>
       </c>
@@ -4648,7 +4709,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>236</v>
       </c>
@@ -4656,7 +4717,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>237</v>
       </c>
@@ -4664,7 +4725,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>238</v>
       </c>
@@ -4672,7 +4733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -4680,7 +4741,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>240</v>
       </c>
@@ -4688,7 +4749,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>241</v>
       </c>
@@ -4696,7 +4757,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>242</v>
       </c>
@@ -4704,7 +4765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>243</v>
       </c>
@@ -4712,7 +4773,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>244</v>
       </c>
@@ -4720,7 +4781,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>245</v>
       </c>
@@ -4728,7 +4789,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>246</v>
       </c>
@@ -4736,7 +4797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>247</v>
       </c>
@@ -4744,7 +4805,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>248</v>
       </c>
@@ -4752,7 +4813,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>587</v>
       </c>
@@ -4760,7 +4821,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>619</v>
       </c>
@@ -4768,7 +4829,18 @@
         <v>620</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>623</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B21" r:id="rId1" xr:uid="{B7A74A7B-F3AA-AF4E-9CA3-F39898492699}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4776,13 +4848,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="23.9453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="23.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -4796,7 +4868,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>249</v>
       </c>
@@ -4810,7 +4882,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>250</v>
       </c>
@@ -4824,7 +4896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>251</v>
       </c>
@@ -4838,7 +4910,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>252</v>
       </c>
@@ -4852,7 +4924,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>253</v>
       </c>
@@ -4866,7 +4938,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>254</v>
       </c>
@@ -4880,7 +4952,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>255</v>
       </c>
@@ -4894,7 +4966,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>256</v>
       </c>
@@ -4908,7 +4980,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>257</v>
       </c>
@@ -4922,7 +4994,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -4936,7 +5008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>259</v>
       </c>
@@ -4950,7 +5022,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>260</v>
       </c>
@@ -4964,7 +5036,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>261</v>
       </c>
@@ -4978,7 +5050,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>262</v>
       </c>
@@ -4992,7 +5064,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -5006,7 +5078,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>264</v>
       </c>
@@ -5020,7 +5092,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>265</v>
       </c>
@@ -5034,7 +5106,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -5048,7 +5120,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>267</v>
       </c>
@@ -5062,7 +5134,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>268</v>
       </c>
@@ -5076,7 +5148,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>269</v>
       </c>
@@ -5090,7 +5162,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -5104,7 +5176,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>271</v>
       </c>
@@ -5118,7 +5190,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>272</v>
       </c>
@@ -5132,7 +5204,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -5146,7 +5218,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -5160,7 +5232,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -5174,7 +5246,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>276</v>
       </c>
@@ -5188,7 +5260,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -5202,7 +5274,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -5216,7 +5288,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>279</v>
       </c>
@@ -5230,7 +5302,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>280</v>
       </c>
@@ -5244,7 +5316,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>281</v>
       </c>
@@ -5258,7 +5330,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -5272,7 +5344,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -5286,7 +5358,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>284</v>
       </c>
@@ -5300,7 +5372,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>285</v>
       </c>
@@ -5314,7 +5386,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>286</v>
       </c>
@@ -5328,7 +5400,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -5342,7 +5414,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>288</v>
       </c>
@@ -5356,7 +5428,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>289</v>
       </c>
@@ -5370,7 +5442,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>290</v>
       </c>
@@ -5384,7 +5456,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -5398,7 +5470,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>292</v>
       </c>
@@ -5412,7 +5484,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -5426,7 +5498,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>294</v>
       </c>
@@ -5440,7 +5512,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>295</v>
       </c>
@@ -5454,7 +5526,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>296</v>
       </c>
@@ -5468,7 +5540,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>297</v>
       </c>
@@ -5482,7 +5554,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>298</v>
       </c>
@@ -5496,7 +5568,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>299</v>
       </c>
@@ -5510,7 +5582,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>300</v>
       </c>
@@ -5524,7 +5596,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>301</v>
       </c>
@@ -5538,7 +5610,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>302</v>
       </c>
@@ -5552,7 +5624,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>303</v>
       </c>
@@ -5566,7 +5638,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>304</v>
       </c>
@@ -5580,7 +5652,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -5594,7 +5666,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>306</v>
       </c>
@@ -5608,7 +5680,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>307</v>
       </c>
@@ -5622,7 +5694,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>308</v>
       </c>
@@ -5636,7 +5708,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>309</v>
       </c>
@@ -5650,7 +5722,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>310</v>
       </c>
@@ -5664,7 +5736,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>311</v>
       </c>
@@ -5678,7 +5750,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>312</v>
       </c>
@@ -5692,7 +5764,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>313</v>
       </c>
@@ -5706,7 +5778,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>314</v>
       </c>
@@ -5720,7 +5792,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>315</v>
       </c>
@@ -5734,7 +5806,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>316</v>
       </c>
@@ -5748,7 +5820,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>317</v>
       </c>
@@ -5762,7 +5834,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>318</v>
       </c>
@@ -5776,7 +5848,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>319</v>
       </c>
@@ -5790,7 +5862,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>320</v>
       </c>
@@ -5804,7 +5876,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>321</v>
       </c>
@@ -5818,7 +5890,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>322</v>
       </c>
@@ -5832,7 +5904,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>323</v>
       </c>
@@ -5846,7 +5918,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>324</v>
       </c>
@@ -5860,7 +5932,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>325</v>
       </c>
@@ -5874,7 +5946,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>326</v>
       </c>
@@ -5888,7 +5960,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>327</v>
       </c>
@@ -5902,7 +5974,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>328</v>
       </c>
@@ -5916,7 +5988,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>329</v>
       </c>
@@ -5930,7 +6002,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>330</v>
       </c>
@@ -5944,7 +6016,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>331</v>
       </c>
@@ -5958,7 +6030,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>332</v>
       </c>
@@ -5972,7 +6044,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>333</v>
       </c>
@@ -5986,7 +6058,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>334</v>
       </c>
@@ -6000,7 +6072,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>335</v>
       </c>
@@ -6014,7 +6086,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>336</v>
       </c>
@@ -6028,7 +6100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>337</v>
       </c>
@@ -6042,7 +6114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>338</v>
       </c>
@@ -6056,7 +6128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>339</v>
       </c>
@@ -6070,7 +6142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>340</v>
       </c>
@@ -6084,7 +6156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>341</v>
       </c>
@@ -6098,7 +6170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>342</v>
       </c>
@@ -6112,7 +6184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>343</v>
       </c>
@@ -6126,7 +6198,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>589</v>
       </c>
@@ -6140,7 +6212,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>615</v>
       </c>
@@ -6163,14 +6235,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E061927E-DAF7-4362-80C4-8054C331DDF2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.390625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6181,7 +6253,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>614</v>
       </c>
@@ -6200,9 +6272,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6210,7 +6282,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>344</v>
       </c>
@@ -6218,7 +6290,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -6226,7 +6298,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -6234,7 +6306,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>347</v>
       </c>
@@ -6242,7 +6314,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>348</v>
       </c>
@@ -6250,7 +6322,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>349</v>
       </c>
@@ -6258,7 +6330,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>350</v>
       </c>
@@ -6266,7 +6338,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>351</v>
       </c>
@@ -6274,7 +6346,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>352</v>
       </c>
@@ -6282,7 +6354,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>353</v>
       </c>
@@ -6290,7 +6362,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>354</v>
       </c>
@@ -6298,7 +6370,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -6306,7 +6378,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>355</v>
       </c>
@@ -6314,7 +6386,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>356</v>
       </c>
@@ -6322,7 +6394,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>357</v>
       </c>
@@ -6330,7 +6402,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>358</v>
       </c>
@@ -6338,7 +6410,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>359</v>
       </c>
@@ -6353,10 +6425,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="23.80859375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6364,7 +6439,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>360</v>
       </c>
@@ -6372,7 +6447,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>361</v>
       </c>
@@ -6380,7 +6455,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>362</v>
       </c>
@@ -6388,17 +6463,31 @@
         <v>113</v>
       </c>
     </row>
+    <row r="5" spans="1:2" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>626</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{34B8F9A4-4FEB-7B47-9E8A-CEA511A3FCD1}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25.828125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6406,7 +6495,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>363</v>
       </c>
@@ -6414,7 +6503,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>364</v>
       </c>
@@ -6422,7 +6511,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>365</v>
       </c>
@@ -6430,17 +6519,31 @@
         <v>100</v>
       </c>
     </row>
+    <row r="5" spans="1:2" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>624</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{62398EEF-A5E5-B444-B3C4-69DED4DC8648}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="26.09765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6448,7 +6551,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>366</v>
       </c>
@@ -6456,7 +6559,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>367</v>
       </c>
@@ -6464,7 +6567,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>368</v>
       </c>
@@ -6472,7 +6575,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -6480,7 +6583,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -6488,7 +6591,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>371</v>
       </c>
@@ -6496,7 +6599,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>372</v>
       </c>
@@ -6504,7 +6607,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>373</v>
       </c>
@@ -6512,7 +6615,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>374</v>
       </c>
@@ -6520,7 +6623,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>375</v>
       </c>
@@ -6528,7 +6631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>376</v>
       </c>
@@ -6536,7 +6639,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>348</v>
       </c>
@@ -6544,7 +6647,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>603</v>
       </c>
@@ -6552,7 +6655,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>605</v>
       </c>
@@ -6560,7 +6663,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>617</v>
       </c>
@@ -6568,7 +6671,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>621</v>
       </c>
@@ -6576,7 +6679,18 @@
         <v>622</v>
       </c>
     </row>
+    <row r="18" spans="1:2" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>625</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B18" r:id="rId1" xr:uid="{33137A18-A892-0847-B660-989BDB1BBA5F}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6584,9 +6698,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6594,7 +6708,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>377</v>
       </c>
@@ -6602,7 +6716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>378</v>
       </c>
@@ -6610,7 +6724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>379</v>
       </c>
@@ -6618,7 +6732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -6626,7 +6740,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>381</v>
       </c>
@@ -6634,7 +6748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>382</v>
       </c>
@@ -6642,7 +6756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>383</v>
       </c>
@@ -6650,7 +6764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>384</v>
       </c>
@@ -6658,7 +6772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>385</v>
       </c>
@@ -6666,7 +6780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>386</v>
       </c>
@@ -6674,7 +6788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>387</v>
       </c>
@@ -6682,7 +6796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>388</v>
       </c>
@@ -6690,7 +6804,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>389</v>
       </c>
@@ -6698,7 +6812,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>390</v>
       </c>
@@ -6706,7 +6820,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>391</v>
       </c>
@@ -6714,7 +6828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>392</v>
       </c>
@@ -6722,7 +6836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>393</v>
       </c>
@@ -6730,7 +6844,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>394</v>
       </c>
@@ -6738,7 +6852,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>395</v>
       </c>
@@ -6746,7 +6860,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>396</v>
       </c>
@@ -6754,7 +6868,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>397</v>
       </c>
@@ -6762,7 +6876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>398</v>
       </c>
@@ -6770,7 +6884,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>399</v>
       </c>
@@ -6778,7 +6892,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>400</v>
       </c>
@@ -6786,7 +6900,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>401</v>
       </c>
@@ -6794,7 +6908,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>402</v>
       </c>
@@ -6802,7 +6916,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>403</v>
       </c>
@@ -6810,7 +6924,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>404</v>
       </c>
@@ -6818,7 +6932,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>405</v>
       </c>
@@ -6826,7 +6940,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>406</v>
       </c>
@@ -6834,7 +6948,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>407</v>
       </c>
@@ -6842,7 +6956,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>408</v>
       </c>
@@ -6850,7 +6964,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>409</v>
       </c>
@@ -6858,7 +6972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>410</v>
       </c>
@@ -6866,7 +6980,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>411</v>
       </c>

--- a/Dataset_BeybladeParts_Final_Images.xlsx
+++ b/Dataset_BeybladeParts_Final_Images.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E1439A-FE33-41F0-9D5C-3E70CA2C0482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BDE5CD2-4261-4F2F-AE6F-963A78342FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="640">
   <si>
     <t>https://i.ibb.co/dJwV04CQ/Vortex.png</t>
   </si>
@@ -1933,19 +1933,37 @@
     <t>GU</t>
   </si>
   <si>
-    <t>https://i.ibb.co/WNXdZTmc/IMG-7496.jpg</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/QzFTs2j/IMG-7491.jpg</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/DP9JDrRj/IMG-7492.jpg</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/KjRGwBFj/IMG-7494.jpg</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/7tbGH5FS/IMG-7493.jpg</t>
+    <t>https://i.ibb.co/KxDJ5dR3/odd.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/4Z0LpSnR/unicorn.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Q7hxYQJG/IMG-7491.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/0v4y5yN/Delta.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/S490TyGR/gearunite.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Cstpj2wP/Right-Spin-Beyblade-X.png</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/G4kh7v5p/Left-Spin-logo-Beyblade-X.webp</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/0jsP3PBc/Unique-Line-Logo-Copy.webp</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/vxNzdd2V/Expand-Infinity.webp</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/NnZDr3NW/Basic-Line-Logo-Copy-1.webp</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/rf35rytJ/Custom-Line.png</t>
   </si>
 </sst>
 </file>
@@ -1990,12 +2008,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2300,1164 +2314,1164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A232"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>229</v>
       </c>
@@ -3470,13 +3484,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>412</v>
       </c>
@@ -3487,7 +3501,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>415</v>
       </c>
@@ -3498,7 +3512,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>417</v>
       </c>
@@ -3509,7 +3523,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>419</v>
       </c>
@@ -3520,7 +3534,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>421</v>
       </c>
@@ -3531,7 +3545,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>423</v>
       </c>
@@ -3542,7 +3556,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>425</v>
       </c>
@@ -3553,7 +3567,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>427</v>
       </c>
@@ -3564,7 +3578,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>429</v>
       </c>
@@ -3575,7 +3589,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>431</v>
       </c>
@@ -3586,7 +3600,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>433</v>
       </c>
@@ -3597,7 +3611,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>435</v>
       </c>
@@ -3608,7 +3622,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>437</v>
       </c>
@@ -3619,7 +3633,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>439</v>
       </c>
@@ -3630,7 +3644,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>441</v>
       </c>
@@ -3641,7 +3655,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>443</v>
       </c>
@@ -3652,7 +3666,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>445</v>
       </c>
@@ -3663,7 +3677,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>447</v>
       </c>
@@ -3674,7 +3688,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>449</v>
       </c>
@@ -3685,7 +3699,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>451</v>
       </c>
@@ -3696,7 +3710,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>453</v>
       </c>
@@ -3707,7 +3721,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>455</v>
       </c>
@@ -3718,7 +3732,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>457</v>
       </c>
@@ -3729,7 +3743,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>459</v>
       </c>
@@ -3740,7 +3754,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>461</v>
       </c>
@@ -3751,7 +3765,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>463</v>
       </c>
@@ -3762,7 +3776,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>465</v>
       </c>
@@ -3773,7 +3787,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>467</v>
       </c>
@@ -3784,7 +3798,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>469</v>
       </c>
@@ -3795,7 +3809,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>471</v>
       </c>
@@ -3806,7 +3820,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>473</v>
       </c>
@@ -3817,7 +3831,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>475</v>
       </c>
@@ -3828,7 +3842,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>477</v>
       </c>
@@ -3839,7 +3853,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>479</v>
       </c>
@@ -3850,7 +3864,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>481</v>
       </c>
@@ -3861,7 +3875,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>483</v>
       </c>
@@ -3872,7 +3886,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>485</v>
       </c>
@@ -3883,7 +3897,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>487</v>
       </c>
@@ -3894,7 +3908,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>489</v>
       </c>
@@ -3905,7 +3919,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>491</v>
       </c>
@@ -3916,7 +3930,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>493</v>
       </c>
@@ -3927,7 +3941,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>495</v>
       </c>
@@ -3938,7 +3952,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>497</v>
       </c>
@@ -3949,7 +3963,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>499</v>
       </c>
@@ -3960,7 +3974,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>501</v>
       </c>
@@ -3971,7 +3985,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>591</v>
       </c>
@@ -3982,7 +3996,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>607</v>
       </c>
@@ -3993,7 +4007,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>608</v>
       </c>
@@ -4004,12 +4018,12 @@
         <v>612</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>627</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>632</v>
+      <c r="B49" t="s">
+        <v>633</v>
       </c>
       <c r="C49" t="s">
         <v>628</v>
@@ -4025,65 +4039,98 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>512</v>
+      </c>
+      <c r="B11" t="s">
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -4094,12 +4141,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>513</v>
       </c>
@@ -4107,7 +4154,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>515</v>
       </c>
@@ -4115,7 +4162,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>517</v>
       </c>
@@ -4123,7 +4170,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>519</v>
       </c>
@@ -4131,7 +4178,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>520</v>
       </c>
@@ -4139,7 +4186,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>521</v>
       </c>
@@ -4147,7 +4194,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>522</v>
       </c>
@@ -4155,7 +4202,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>523</v>
       </c>
@@ -4163,7 +4210,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>524</v>
       </c>
@@ -4171,7 +4218,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>525</v>
       </c>
@@ -4179,7 +4226,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>526</v>
       </c>
@@ -4187,7 +4234,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>527</v>
       </c>
@@ -4195,7 +4242,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>528</v>
       </c>
@@ -4203,7 +4250,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>529</v>
       </c>
@@ -4211,7 +4258,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>530</v>
       </c>
@@ -4219,7 +4266,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>531</v>
       </c>
@@ -4227,7 +4274,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>532</v>
       </c>
@@ -4235,7 +4282,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>533</v>
       </c>
@@ -4243,7 +4290,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>534</v>
       </c>
@@ -4251,7 +4298,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>535</v>
       </c>
@@ -4259,7 +4306,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>536</v>
       </c>
@@ -4267,7 +4314,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>537</v>
       </c>
@@ -4275,7 +4322,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>538</v>
       </c>
@@ -4283,7 +4330,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>539</v>
       </c>
@@ -4291,7 +4338,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>540</v>
       </c>
@@ -4299,7 +4346,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>541</v>
       </c>
@@ -4307,7 +4354,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>542</v>
       </c>
@@ -4315,7 +4362,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>543</v>
       </c>
@@ -4323,7 +4370,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>544</v>
       </c>
@@ -4331,7 +4378,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>545</v>
       </c>
@@ -4339,7 +4386,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>546</v>
       </c>
@@ -4347,7 +4394,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>547</v>
       </c>
@@ -4355,7 +4402,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>548</v>
       </c>
@@ -4363,7 +4410,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>549</v>
       </c>
@@ -4371,7 +4418,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>550</v>
       </c>
@@ -4379,7 +4426,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>551</v>
       </c>
@@ -4387,7 +4434,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>552</v>
       </c>
@@ -4395,7 +4442,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>553</v>
       </c>
@@ -4403,7 +4450,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>554</v>
       </c>
@@ -4411,7 +4458,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>555</v>
       </c>
@@ -4419,7 +4466,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>556</v>
       </c>
@@ -4427,7 +4474,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>557</v>
       </c>
@@ -4435,7 +4482,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>558</v>
       </c>
@@ -4443,7 +4490,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>559</v>
       </c>
@@ -4451,7 +4498,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>560</v>
       </c>
@@ -4459,7 +4506,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>561</v>
       </c>
@@ -4467,7 +4514,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>562</v>
       </c>
@@ -4475,7 +4522,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>563</v>
       </c>
@@ -4483,7 +4530,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>564</v>
       </c>
@@ -4491,7 +4538,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>565</v>
       </c>
@@ -4499,7 +4546,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>566</v>
       </c>
@@ -4507,7 +4554,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>567</v>
       </c>
@@ -4515,7 +4562,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>568</v>
       </c>
@@ -4523,7 +4570,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>569</v>
       </c>
@@ -4531,7 +4578,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>570</v>
       </c>
@@ -4539,7 +4586,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>571</v>
       </c>
@@ -4547,7 +4594,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>572</v>
       </c>
@@ -4555,7 +4602,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>573</v>
       </c>
@@ -4563,7 +4610,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>574</v>
       </c>
@@ -4571,7 +4618,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>575</v>
       </c>
@@ -4579,7 +4626,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>576</v>
       </c>
@@ -4587,7 +4634,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>577</v>
       </c>
@@ -4595,7 +4642,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>578</v>
       </c>
@@ -4603,7 +4650,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>579</v>
       </c>
@@ -4611,7 +4658,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>580</v>
       </c>
@@ -4619,7 +4666,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>581</v>
       </c>
@@ -4627,7 +4674,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>582</v>
       </c>
@@ -4635,7 +4682,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>583</v>
       </c>
@@ -4643,7 +4690,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>584</v>
       </c>
@@ -4651,7 +4698,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>585</v>
       </c>
@@ -4667,9 +4714,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -4677,7 +4724,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>232</v>
       </c>
@@ -4685,7 +4732,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>233</v>
       </c>
@@ -4693,7 +4740,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>234</v>
       </c>
@@ -4701,7 +4748,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>235</v>
       </c>
@@ -4709,7 +4756,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>236</v>
       </c>
@@ -4717,7 +4764,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>237</v>
       </c>
@@ -4725,7 +4772,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>238</v>
       </c>
@@ -4733,7 +4780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -4741,7 +4788,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>240</v>
       </c>
@@ -4749,7 +4796,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>241</v>
       </c>
@@ -4757,7 +4804,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>242</v>
       </c>
@@ -4765,7 +4812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>243</v>
       </c>
@@ -4773,7 +4820,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>244</v>
       </c>
@@ -4781,7 +4828,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>245</v>
       </c>
@@ -4789,7 +4836,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>246</v>
       </c>
@@ -4797,7 +4844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>247</v>
       </c>
@@ -4805,7 +4852,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>248</v>
       </c>
@@ -4813,7 +4860,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>587</v>
       </c>
@@ -4821,7 +4868,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>619</v>
       </c>
@@ -4829,12 +4876,12 @@
         <v>620</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>623</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>629</v>
+      <c r="B21" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -4848,13 +4895,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.9453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="23.9453125" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -4868,7 +4915,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>249</v>
       </c>
@@ -4882,7 +4929,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>250</v>
       </c>
@@ -4896,7 +4943,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>251</v>
       </c>
@@ -4910,7 +4957,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>252</v>
       </c>
@@ -4924,7 +4971,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>253</v>
       </c>
@@ -4938,7 +4985,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>254</v>
       </c>
@@ -4952,7 +4999,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>255</v>
       </c>
@@ -4966,7 +5013,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>256</v>
       </c>
@@ -4980,7 +5027,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>257</v>
       </c>
@@ -4994,7 +5041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -5008,7 +5055,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>259</v>
       </c>
@@ -5022,7 +5069,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>260</v>
       </c>
@@ -5036,7 +5083,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>261</v>
       </c>
@@ -5050,7 +5097,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>262</v>
       </c>
@@ -5064,7 +5111,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -5078,7 +5125,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>264</v>
       </c>
@@ -5092,7 +5139,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>265</v>
       </c>
@@ -5106,7 +5153,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -5120,7 +5167,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>267</v>
       </c>
@@ -5134,7 +5181,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>268</v>
       </c>
@@ -5148,7 +5195,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>269</v>
       </c>
@@ -5162,7 +5209,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -5176,7 +5223,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>271</v>
       </c>
@@ -5190,7 +5237,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>272</v>
       </c>
@@ -5204,7 +5251,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -5218,7 +5265,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>274</v>
       </c>
@@ -5232,7 +5279,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -5246,7 +5293,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>276</v>
       </c>
@@ -5260,7 +5307,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -5274,7 +5321,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -5288,7 +5335,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>279</v>
       </c>
@@ -5302,7 +5349,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>280</v>
       </c>
@@ -5316,7 +5363,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>281</v>
       </c>
@@ -5330,7 +5377,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -5344,7 +5391,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -5358,7 +5405,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>284</v>
       </c>
@@ -5372,7 +5419,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>285</v>
       </c>
@@ -5386,7 +5433,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5447,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -5414,7 +5461,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>288</v>
       </c>
@@ -5428,7 +5475,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>289</v>
       </c>
@@ -5442,7 +5489,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>290</v>
       </c>
@@ -5456,7 +5503,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -5470,7 +5517,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>292</v>
       </c>
@@ -5484,7 +5531,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -5498,7 +5545,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>294</v>
       </c>
@@ -5512,7 +5559,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>295</v>
       </c>
@@ -5526,7 +5573,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>296</v>
       </c>
@@ -5540,7 +5587,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>297</v>
       </c>
@@ -5554,7 +5601,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>298</v>
       </c>
@@ -5568,7 +5615,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>299</v>
       </c>
@@ -5582,7 +5629,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>300</v>
       </c>
@@ -5596,7 +5643,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>301</v>
       </c>
@@ -5610,7 +5657,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>302</v>
       </c>
@@ -5624,7 +5671,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>303</v>
       </c>
@@ -5638,7 +5685,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>304</v>
       </c>
@@ -5652,7 +5699,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>305</v>
       </c>
@@ -5666,7 +5713,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>306</v>
       </c>
@@ -5680,7 +5727,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>307</v>
       </c>
@@ -5694,7 +5741,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>308</v>
       </c>
@@ -5708,7 +5755,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>309</v>
       </c>
@@ -5722,7 +5769,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>310</v>
       </c>
@@ -5736,7 +5783,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>311</v>
       </c>
@@ -5750,7 +5797,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>312</v>
       </c>
@@ -5764,7 +5811,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>313</v>
       </c>
@@ -5778,7 +5825,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>314</v>
       </c>
@@ -5792,7 +5839,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>315</v>
       </c>
@@ -5806,7 +5853,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>316</v>
       </c>
@@ -5820,7 +5867,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>317</v>
       </c>
@@ -5834,7 +5881,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>318</v>
       </c>
@@ -5848,7 +5895,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>319</v>
       </c>
@@ -5862,7 +5909,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>320</v>
       </c>
@@ -5876,7 +5923,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>321</v>
       </c>
@@ -5890,7 +5937,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>322</v>
       </c>
@@ -5904,7 +5951,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>323</v>
       </c>
@@ -5918,7 +5965,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>324</v>
       </c>
@@ -5932,7 +5979,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>325</v>
       </c>
@@ -5946,7 +5993,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>326</v>
       </c>
@@ -5960,7 +6007,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>327</v>
       </c>
@@ -5974,7 +6021,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>328</v>
       </c>
@@ -5988,7 +6035,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>329</v>
       </c>
@@ -6002,7 +6049,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>330</v>
       </c>
@@ -6016,7 +6063,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>331</v>
       </c>
@@ -6030,7 +6077,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>332</v>
       </c>
@@ -6044,7 +6091,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>333</v>
       </c>
@@ -6058,7 +6105,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>334</v>
       </c>
@@ -6072,7 +6119,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>335</v>
       </c>
@@ -6086,7 +6133,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>336</v>
       </c>
@@ -6100,7 +6147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>337</v>
       </c>
@@ -6114,7 +6161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>338</v>
       </c>
@@ -6128,7 +6175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>339</v>
       </c>
@@ -6142,7 +6189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>340</v>
       </c>
@@ -6156,7 +6203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>341</v>
       </c>
@@ -6170,7 +6217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>342</v>
       </c>
@@ -6184,7 +6231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>343</v>
       </c>
@@ -6198,7 +6245,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>589</v>
       </c>
@@ -6212,7 +6259,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>615</v>
       </c>
@@ -6235,14 +6282,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E061927E-DAF7-4362-80C4-8054C331DDF2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.390625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6253,7 +6300,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>614</v>
       </c>
@@ -6272,9 +6319,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6282,7 +6329,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>344</v>
       </c>
@@ -6290,7 +6337,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -6298,7 +6345,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -6306,7 +6353,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>347</v>
       </c>
@@ -6314,7 +6361,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>348</v>
       </c>
@@ -6322,7 +6369,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>349</v>
       </c>
@@ -6330,7 +6377,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>350</v>
       </c>
@@ -6338,7 +6385,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>351</v>
       </c>
@@ -6346,7 +6393,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>352</v>
       </c>
@@ -6354,7 +6401,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>353</v>
       </c>
@@ -6362,7 +6409,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>354</v>
       </c>
@@ -6370,7 +6417,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -6378,7 +6425,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>355</v>
       </c>
@@ -6386,7 +6433,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>356</v>
       </c>
@@ -6394,7 +6441,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>357</v>
       </c>
@@ -6402,7 +6449,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>358</v>
       </c>
@@ -6410,7 +6457,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>359</v>
       </c>
@@ -6426,12 +6473,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.80859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6439,7 +6486,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>360</v>
       </c>
@@ -6447,7 +6494,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>361</v>
       </c>
@@ -6455,7 +6502,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>362</v>
       </c>
@@ -6463,12 +6510,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>626</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>630</v>
+      <c r="B5" t="s">
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -6482,12 +6529,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6495,7 +6542,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>363</v>
       </c>
@@ -6503,7 +6550,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>364</v>
       </c>
@@ -6511,7 +6558,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>365</v>
       </c>
@@ -6519,12 +6566,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>624</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>631</v>
+      <c r="B5" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -6538,12 +6585,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6551,7 +6598,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>366</v>
       </c>
@@ -6559,7 +6606,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>367</v>
       </c>
@@ -6567,7 +6614,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>368</v>
       </c>
@@ -6575,7 +6622,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -6583,7 +6630,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -6591,7 +6638,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>371</v>
       </c>
@@ -6599,7 +6646,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>372</v>
       </c>
@@ -6607,7 +6654,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>373</v>
       </c>
@@ -6615,7 +6662,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>374</v>
       </c>
@@ -6623,7 +6670,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>375</v>
       </c>
@@ -6631,7 +6678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>376</v>
       </c>
@@ -6639,7 +6686,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>348</v>
       </c>
@@ -6647,7 +6694,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>603</v>
       </c>
@@ -6655,7 +6702,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>605</v>
       </c>
@@ -6663,7 +6710,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>617</v>
       </c>
@@ -6671,7 +6718,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>621</v>
       </c>
@@ -6679,18 +6726,15 @@
         <v>622</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>625</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>633</v>
+      <c r="B18" t="s">
+        <v>629</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B18" r:id="rId1" xr:uid="{33137A18-A892-0847-B660-989BDB1BBA5F}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6698,9 +6742,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -6708,7 +6752,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>377</v>
       </c>
@@ -6716,7 +6760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>378</v>
       </c>
@@ -6724,7 +6768,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>379</v>
       </c>
@@ -6732,7 +6776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -6740,7 +6784,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>381</v>
       </c>
@@ -6748,7 +6792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>382</v>
       </c>
@@ -6756,7 +6800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>383</v>
       </c>
@@ -6764,7 +6808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>384</v>
       </c>
@@ -6772,7 +6816,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>385</v>
       </c>
@@ -6780,7 +6824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>386</v>
       </c>
@@ -6788,7 +6832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>387</v>
       </c>
@@ -6796,7 +6840,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>388</v>
       </c>
@@ -6804,7 +6848,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>389</v>
       </c>
@@ -6812,7 +6856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>390</v>
       </c>
@@ -6820,7 +6864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>391</v>
       </c>
@@ -6828,7 +6872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>392</v>
       </c>
@@ -6836,7 +6880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>393</v>
       </c>
@@ -6844,7 +6888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>394</v>
       </c>
@@ -6852,7 +6896,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>395</v>
       </c>
@@ -6860,7 +6904,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>396</v>
       </c>
@@ -6868,7 +6912,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>397</v>
       </c>
@@ -6876,7 +6920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>398</v>
       </c>
@@ -6884,7 +6928,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>399</v>
       </c>
@@ -6892,7 +6936,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>400</v>
       </c>
@@ -6900,7 +6944,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>401</v>
       </c>
@@ -6908,7 +6952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>402</v>
       </c>
@@ -6916,7 +6960,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>403</v>
       </c>
@@ -6924,7 +6968,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>404</v>
       </c>
@@ -6932,7 +6976,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>405</v>
       </c>
@@ -6940,7 +6984,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>406</v>
       </c>
@@ -6948,7 +6992,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>407</v>
       </c>
@@ -6956,7 +7000,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>408</v>
       </c>
@@ -6964,7 +7008,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>409</v>
       </c>
@@ -6972,7 +7016,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>410</v>
       </c>
@@ -6980,7 +7024,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>411</v>
       </c>
